--- a/artfynd/A 37262-2025 artfynd.xlsx
+++ b/artfynd/A 37262-2025 artfynd.xlsx
@@ -675,42 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131996409</v>
+        <v>131996307</v>
       </c>
       <c r="B2" t="n">
-        <v>57141</v>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534538</v>
+        <v>534631</v>
       </c>
       <c r="R2" t="n">
-        <v>7051696</v>
+        <v>7051735</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,17 +752,13 @@
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spillning, sannolikt av tupp.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131996313</v>
+        <v>131996317</v>
       </c>
       <c r="B3" t="n">
-        <v>79085</v>
+        <v>91970</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,26 +793,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534640</v>
+        <v>534503</v>
       </c>
       <c r="R3" t="n">
-        <v>7051680</v>
+        <v>7051689</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131996428</v>
+        <v>131996427</v>
       </c>
       <c r="B4" t="n">
-        <v>79327</v>
+        <v>91970</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,26 +903,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534452</v>
+        <v>534517</v>
       </c>
       <c r="R4" t="n">
-        <v>7051577</v>
+        <v>7051674</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,32 +1002,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131996414</v>
+        <v>131996318</v>
       </c>
       <c r="B5" t="n">
-        <v>80432</v>
+        <v>92153</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1503</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534504</v>
+        <v>534454</v>
       </c>
       <c r="R5" t="n">
-        <v>7051675</v>
+        <v>7051594</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,21 +1091,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1123,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131996413</v>
+        <v>131996312</v>
       </c>
       <c r="B6" t="n">
-        <v>80432</v>
+        <v>92027</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,26 +1119,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1161,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534511</v>
+        <v>534440</v>
       </c>
       <c r="R6" t="n">
-        <v>7051662</v>
+        <v>7051600</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,21 +1201,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1244,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131996427</v>
+        <v>131996410</v>
       </c>
       <c r="B7" t="n">
-        <v>91905</v>
+        <v>80489</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,30 +1229,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1286,7 +1256,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534517</v>
+        <v>534504</v>
       </c>
       <c r="R7" t="n">
         <v>7051674</v>
@@ -1337,6 +1307,21 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1354,10 +1339,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131996315</v>
+        <v>131996324</v>
       </c>
       <c r="B8" t="n">
-        <v>79085</v>
+        <v>93271</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,26 +1350,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1392,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534645</v>
+        <v>534591</v>
       </c>
       <c r="R8" t="n">
-        <v>7051648</v>
+        <v>7051689</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131996308</v>
+        <v>131996325</v>
       </c>
       <c r="B9" t="n">
-        <v>79946</v>
+        <v>93271</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1471,26 +1460,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1498,10 +1491,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>534651</v>
+        <v>534612</v>
       </c>
       <c r="R9" t="n">
-        <v>7051660</v>
+        <v>7051726</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,32 +1559,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131996306</v>
+        <v>131996319</v>
       </c>
       <c r="B10" t="n">
-        <v>83307</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1604,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>534536</v>
+        <v>534435</v>
       </c>
       <c r="R10" t="n">
-        <v>7051712</v>
+        <v>7051620</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1672,41 +1665,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131996419</v>
+        <v>131996320</v>
       </c>
       <c r="B11" t="n">
-        <v>80432</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1714,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>534490</v>
+        <v>534414</v>
       </c>
       <c r="R11" t="n">
-        <v>7051640</v>
+        <v>7051634</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1752,11 +1741,6 @@
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på en sälg.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1770,21 +1754,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1802,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131996318</v>
+        <v>131996321</v>
       </c>
       <c r="B12" t="n">
-        <v>92083</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1813,21 +1782,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1809,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534454</v>
+        <v>534484</v>
       </c>
       <c r="R12" t="n">
-        <v>7051594</v>
+        <v>7051686</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1908,41 +1877,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131996317</v>
+        <v>131996322</v>
       </c>
       <c r="B13" t="n">
-        <v>91905</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1950,10 +1915,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534503</v>
+        <v>534536</v>
       </c>
       <c r="R13" t="n">
-        <v>7051689</v>
+        <v>7051716</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2018,42 +1983,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131996311</v>
+        <v>131996323</v>
       </c>
       <c r="B14" t="n">
-        <v>57141</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2061,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>534625</v>
+        <v>534617</v>
       </c>
       <c r="R14" t="n">
-        <v>7051694</v>
+        <v>7051696</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2099,17 +2059,13 @@
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Spillning sannolikt från tupp.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2133,32 +2089,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131996404</v>
+        <v>131996428</v>
       </c>
       <c r="B15" t="n">
-        <v>79946</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>534491</v>
+        <v>534452</v>
       </c>
       <c r="R15" t="n">
-        <v>7051605</v>
+        <v>7051577</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2239,32 +2195,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131996416</v>
+        <v>131996429</v>
       </c>
       <c r="B16" t="n">
-        <v>80432</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2277,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>534626</v>
+        <v>534516</v>
       </c>
       <c r="R16" t="n">
-        <v>7051668</v>
+        <v>7051691</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2328,21 +2284,6 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2360,10 +2301,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131996412</v>
+        <v>131996306</v>
       </c>
       <c r="B17" t="n">
-        <v>80432</v>
+        <v>83358</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2371,21 +2312,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2398,10 +2339,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>534496</v>
+        <v>534536</v>
       </c>
       <c r="R17" t="n">
-        <v>7051642</v>
+        <v>7051712</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2449,21 +2390,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2481,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131996424</v>
+        <v>131996421</v>
       </c>
       <c r="B18" t="n">
-        <v>79084</v>
+        <v>79130</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2519,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>534603</v>
+        <v>534447</v>
       </c>
       <c r="R18" t="n">
-        <v>7051606</v>
+        <v>7051605</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2587,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131996418</v>
+        <v>131996422</v>
       </c>
       <c r="B19" t="n">
-        <v>80432</v>
+        <v>79130</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2598,21 +2524,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2625,10 +2551,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>534470</v>
+        <v>534513</v>
       </c>
       <c r="R19" t="n">
-        <v>7051639</v>
+        <v>7051656</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2676,21 +2602,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2708,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131996321</v>
+        <v>131996423</v>
       </c>
       <c r="B20" t="n">
-        <v>79327</v>
+        <v>79130</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2719,21 +2630,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2746,10 +2657,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>534484</v>
+        <v>534609</v>
       </c>
       <c r="R20" t="n">
-        <v>7051686</v>
+        <v>7051605</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2814,10 +2725,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131996312</v>
+        <v>131996424</v>
       </c>
       <c r="B21" t="n">
-        <v>91962</v>
+        <v>79130</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2825,30 +2736,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2856,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>534440</v>
+        <v>534603</v>
       </c>
       <c r="R21" t="n">
-        <v>7051600</v>
+        <v>7051606</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2924,10 +2831,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131996406</v>
+        <v>131996425</v>
       </c>
       <c r="B22" t="n">
-        <v>57953</v>
+        <v>79130</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2935,31 +2842,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2967,10 +2869,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>534469</v>
+        <v>534576</v>
       </c>
       <c r="R22" t="n">
-        <v>7051640</v>
+        <v>7051574</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3005,38 +2907,19 @@
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3054,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131996405</v>
+        <v>131996308</v>
       </c>
       <c r="B23" t="n">
-        <v>79917</v>
+        <v>79992</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3065,21 +2948,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3092,10 +2975,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>534642</v>
+        <v>534651</v>
       </c>
       <c r="R23" t="n">
-        <v>7051607</v>
+        <v>7051660</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3160,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131996423</v>
+        <v>131996309</v>
       </c>
       <c r="B24" t="n">
-        <v>79084</v>
+        <v>79992</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,21 +3054,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3198,10 +3081,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>534609</v>
+        <v>534662</v>
       </c>
       <c r="R24" t="n">
-        <v>7051605</v>
+        <v>7051580</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3266,10 +3149,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131996408</v>
+        <v>131996404</v>
       </c>
       <c r="B25" t="n">
-        <v>57953</v>
+        <v>79992</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3277,31 +3160,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3309,10 +3187,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>534479</v>
+        <v>534491</v>
       </c>
       <c r="R25" t="n">
-        <v>7051649</v>
+        <v>7051605</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3347,38 +3225,19 @@
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3396,10 +3255,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131996407</v>
+        <v>131996412</v>
       </c>
       <c r="B26" t="n">
-        <v>57953</v>
+        <v>80488</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3407,31 +3266,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3439,10 +3293,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>534505</v>
+        <v>534496</v>
       </c>
       <c r="R26" t="n">
-        <v>7051653</v>
+        <v>7051642</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3477,17 +3331,13 @@
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3498,17 +3348,17 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3526,10 +3376,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131996411</v>
+        <v>131996413</v>
       </c>
       <c r="B27" t="n">
-        <v>79085</v>
+        <v>80488</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3537,21 +3387,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3564,10 +3414,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>534487</v>
+        <v>534511</v>
       </c>
       <c r="R27" t="n">
-        <v>7051603</v>
+        <v>7051662</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3619,17 +3469,17 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3647,10 +3497,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131996309</v>
+        <v>131996414</v>
       </c>
       <c r="B28" t="n">
-        <v>79946</v>
+        <v>80488</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3658,21 +3508,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3685,10 +3535,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>534662</v>
+        <v>534504</v>
       </c>
       <c r="R28" t="n">
-        <v>7051580</v>
+        <v>7051675</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3736,6 +3586,21 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3753,10 +3618,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131996310</v>
+        <v>131996415</v>
       </c>
       <c r="B29" t="n">
-        <v>57953</v>
+        <v>80488</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3764,54 +3629,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sundnäset, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>534469</v>
+        <v>534513</v>
       </c>
       <c r="R29" t="n">
-        <v>7051650</v>
+        <v>7051682</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3846,23 +3694,34 @@
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>1st födosökande hane som bl.a. födosökte på en liggande björkstam. Fyndplatsen finns i en i en yta med högt livsmiljövärde för tretåig hackspett baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3880,10 +3739,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131996415</v>
+        <v>131996416</v>
       </c>
       <c r="B30" t="n">
-        <v>80432</v>
+        <v>80488</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3918,10 +3777,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>534513</v>
+        <v>534626</v>
       </c>
       <c r="R30" t="n">
-        <v>7051682</v>
+        <v>7051668</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4001,10 +3860,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131996323</v>
+        <v>131996418</v>
       </c>
       <c r="B31" t="n">
-        <v>79327</v>
+        <v>80488</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4012,21 +3871,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4039,10 +3898,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>534617</v>
+        <v>534470</v>
       </c>
       <c r="R31" t="n">
-        <v>7051696</v>
+        <v>7051639</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4090,6 +3949,21 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4107,10 +3981,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131996319</v>
+        <v>131996419</v>
       </c>
       <c r="B32" t="n">
-        <v>79327</v>
+        <v>80488</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4118,26 +3992,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4145,10 +4023,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>534435</v>
+        <v>534490</v>
       </c>
       <c r="R32" t="n">
-        <v>7051620</v>
+        <v>7051640</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4183,6 +4061,11 @@
           <t>2026-03-25</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på en sälg.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4196,6 +4079,21 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4213,10 +4111,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131996422</v>
+        <v>131996420</v>
       </c>
       <c r="B33" t="n">
-        <v>79084</v>
+        <v>80488</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4224,21 +4122,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4251,10 +4149,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>534513</v>
+        <v>534650</v>
       </c>
       <c r="R33" t="n">
-        <v>7051656</v>
+        <v>7051629</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4302,6 +4200,21 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4319,10 +4232,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131996410</v>
+        <v>131996310</v>
       </c>
       <c r="B34" t="n">
-        <v>80433</v>
+        <v>57975</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4330,37 +4243,54 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sundnäset, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>534504</v>
+        <v>534469</v>
       </c>
       <c r="R34" t="n">
-        <v>7051674</v>
+        <v>7051650</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4395,34 +4325,23 @@
           <t>2026-03-25</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>1st födosökande hane som bl.a. födosökte på en liggande björkstam. Fyndplatsen finns i en i en yta med högt livsmiljövärde för tretåig hackspett baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4440,39 +4359,40 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131996324</v>
+        <v>131996406</v>
       </c>
       <c r="B35" t="n">
-        <v>93197</v>
+        <v>57975</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4482,10 +4402,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>534591</v>
+        <v>534469</v>
       </c>
       <c r="R35" t="n">
-        <v>7051689</v>
+        <v>7051640</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4520,19 +4440,38 @@
           <t>2026-03-25</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4550,10 +4489,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131996316</v>
+        <v>131996407</v>
       </c>
       <c r="B36" t="n">
-        <v>57132</v>
+        <v>57975</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4561,16 +4500,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4578,33 +4517,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sundnäset, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>534529</v>
+        <v>534505</v>
       </c>
       <c r="R36" t="n">
-        <v>7051719</v>
+        <v>7051653</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4639,6 +4570,11 @@
           <t>2026-03-25</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4651,6 +4587,21 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4668,10 +4619,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131996320</v>
+        <v>131996408</v>
       </c>
       <c r="B37" t="n">
-        <v>79327</v>
+        <v>57975</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4679,26 +4630,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4706,10 +4662,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>534414</v>
+        <v>534479</v>
       </c>
       <c r="R37" t="n">
-        <v>7051634</v>
+        <v>7051649</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4744,19 +4700,38 @@
           <t>2026-03-25</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4774,37 +4749,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131996322</v>
+        <v>131996311</v>
       </c>
       <c r="B38" t="n">
-        <v>79327</v>
+        <v>57162</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4812,10 +4792,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>534536</v>
+        <v>534625</v>
       </c>
       <c r="R38" t="n">
-        <v>7051716</v>
+        <v>7051694</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4850,13 +4830,17 @@
           <t>2026-03-25</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Spillning sannolikt från tupp.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4880,10 +4864,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131996325</v>
+        <v>131996409</v>
       </c>
       <c r="B39" t="n">
-        <v>93197</v>
+        <v>57162</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4891,28 +4875,29 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4922,10 +4907,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>534612</v>
+        <v>534538</v>
       </c>
       <c r="R39" t="n">
-        <v>7051726</v>
+        <v>7051696</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4960,13 +4945,17 @@
           <t>2026-03-25</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Spillning, sannolikt av tupp.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4990,48 +4979,61 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131996429</v>
+        <v>131996316</v>
       </c>
       <c r="B40" t="n">
-        <v>79327</v>
+        <v>57153</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sundnäset, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>534516</v>
+        <v>534529</v>
       </c>
       <c r="R40" t="n">
-        <v>7051691</v>
+        <v>7051719</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5072,7 +5074,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5096,48 +5097,57 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131996420</v>
+        <v>131996426</v>
       </c>
       <c r="B41" t="n">
-        <v>80432</v>
+        <v>57153</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sundnäset, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>534650</v>
+        <v>534621</v>
       </c>
       <c r="R41" t="n">
-        <v>7051629</v>
+        <v>7051679</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5172,13 +5182,17 @@
           <t>2026-03-25</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>1 stillasittande individ av järpe som skrämdes upp.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5187,19 +5201,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Bitvis tätare grandominerade partier som omges av blockrik tallskog.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5217,10 +5221,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131996425</v>
+        <v>131996313</v>
       </c>
       <c r="B42" t="n">
-        <v>79084</v>
+        <v>79131</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5228,21 +5232,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5255,10 +5259,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>534576</v>
+        <v>534640</v>
       </c>
       <c r="R42" t="n">
-        <v>7051574</v>
+        <v>7051680</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5323,10 +5327,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131996421</v>
+        <v>131996314</v>
       </c>
       <c r="B43" t="n">
-        <v>79084</v>
+        <v>79131</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5334,21 +5338,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5361,10 +5365,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>534447</v>
+        <v>534650</v>
       </c>
       <c r="R43" t="n">
-        <v>7051605</v>
+        <v>7051669</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5429,10 +5433,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131996307</v>
+        <v>131996315</v>
       </c>
       <c r="B44" t="n">
-        <v>97358</v>
+        <v>79131</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5440,27 +5444,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5468,10 +5471,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>534631</v>
+        <v>534645</v>
       </c>
       <c r="R44" t="n">
-        <v>7051735</v>
+        <v>7051648</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5536,10 +5539,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131996314</v>
+        <v>131996411</v>
       </c>
       <c r="B45" t="n">
-        <v>79085</v>
+        <v>79131</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5574,10 +5577,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>534650</v>
+        <v>534487</v>
       </c>
       <c r="R45" t="n">
-        <v>7051669</v>
+        <v>7051603</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5625,6 +5628,21 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5642,10 +5660,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131996426</v>
+        <v>131996405</v>
       </c>
       <c r="B46" t="n">
-        <v>57132</v>
+        <v>79963</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5653,46 +5671,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102612</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sundnäset, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>534621</v>
+        <v>534642</v>
       </c>
       <c r="R46" t="n">
-        <v>7051679</v>
+        <v>7051607</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5727,28 +5736,19 @@
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>1 stillasittande individ av järpe som skrämdes upp.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Bitvis tätare grandominerade partier som omges av blockrik tallskog.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>

--- a/artfynd/A 37262-2025 artfynd.xlsx
+++ b/artfynd/A 37262-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AZ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996307</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996317</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996427</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996318</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996312</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1336,6 +1366,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996410</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1446,6 +1481,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996324</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1556,6 +1596,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996325</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1662,6 +1707,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996319</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1768,6 +1818,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996320</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1874,6 +1929,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996321</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1980,6 +2040,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996322</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2086,6 +2151,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996323</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2192,6 +2262,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996428</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2298,6 +2373,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996429</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2404,6 +2484,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996306</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2510,6 +2595,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996421</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2616,6 +2706,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996422</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2722,6 +2817,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996423</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2828,6 +2928,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996424</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2934,6 +3039,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996425</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3040,6 +3150,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996308</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3146,6 +3261,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996309</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3252,6 +3372,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996404</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3373,6 +3498,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996412</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3494,6 +3624,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996413</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3615,6 +3750,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996414</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3736,6 +3876,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996415</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3857,6 +4002,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996416</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3978,6 +4128,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996418</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4108,6 +4263,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996419</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4229,6 +4389,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996420</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4356,6 +4521,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996310</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4486,6 +4656,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996406</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4616,6 +4791,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996407</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4746,6 +4926,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996408</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4861,6 +5046,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996311</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4976,6 +5166,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996409</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5094,6 +5289,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996316</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5218,6 +5418,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996426</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5324,6 +5529,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996313</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5430,6 +5640,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996314</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5536,6 +5751,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996315</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5657,6 +5877,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996411</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5763,8 +5988,60 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996405</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>